--- a/artfynd/A 52894-2025 artfynd.xlsx
+++ b/artfynd/A 52894-2025 artfynd.xlsx
@@ -1102,7 +1102,7 @@
         <v>129688629</v>
       </c>
       <c r="B6" t="n">
-        <v>98757</v>
+        <v>98768</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 52894-2025 artfynd.xlsx
+++ b/artfynd/A 52894-2025 artfynd.xlsx
@@ -1102,7 +1102,7 @@
         <v>129688629</v>
       </c>
       <c r="B6" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 52894-2025 artfynd.xlsx
+++ b/artfynd/A 52894-2025 artfynd.xlsx
@@ -1102,7 +1102,7 @@
         <v>129688629</v>
       </c>
       <c r="B6" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 52894-2025 artfynd.xlsx
+++ b/artfynd/A 52894-2025 artfynd.xlsx
@@ -1102,7 +1102,7 @@
         <v>129688629</v>
       </c>
       <c r="B6" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 52894-2025 artfynd.xlsx
+++ b/artfynd/A 52894-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1102,7 +1102,7 @@
         <v>129688629</v>
       </c>
       <c r="B6" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,6 +1202,121 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129866836</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98780</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stockuddens barrskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>515387</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6522665</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>E-Mot-0249</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Karin Nyström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52894-2025 artfynd.xlsx
+++ b/artfynd/A 52894-2025 artfynd.xlsx
@@ -1102,7 +1102,7 @@
         <v>129688629</v>
       </c>
       <c r="B6" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>129866836</v>
       </c>
       <c r="B7" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 52894-2025 artfynd.xlsx
+++ b/artfynd/A 52894-2025 artfynd.xlsx
@@ -1208,7 +1208,7 @@
         <v>129866836</v>
       </c>
       <c r="B7" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 52894-2025 artfynd.xlsx
+++ b/artfynd/A 52894-2025 artfynd.xlsx
@@ -1102,7 +1102,7 @@
         <v>129688629</v>
       </c>
       <c r="B6" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 52894-2025 artfynd.xlsx
+++ b/artfynd/A 52894-2025 artfynd.xlsx
@@ -1102,7 +1102,7 @@
         <v>129688629</v>
       </c>
       <c r="B6" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>129866836</v>
       </c>
       <c r="B7" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 52894-2025 artfynd.xlsx
+++ b/artfynd/A 52894-2025 artfynd.xlsx
@@ -1102,7 +1102,7 @@
         <v>129688629</v>
       </c>
       <c r="B6" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>129866836</v>
       </c>
       <c r="B7" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 52894-2025 artfynd.xlsx
+++ b/artfynd/A 52894-2025 artfynd.xlsx
@@ -1102,7 +1102,7 @@
         <v>129688629</v>
       </c>
       <c r="B6" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>129866836</v>
       </c>
       <c r="B7" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 52894-2025 artfynd.xlsx
+++ b/artfynd/A 52894-2025 artfynd.xlsx
@@ -1208,7 +1208,7 @@
         <v>129866836</v>
       </c>
       <c r="B7" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 52894-2025 artfynd.xlsx
+++ b/artfynd/A 52894-2025 artfynd.xlsx
@@ -1208,7 +1208,7 @@
         <v>129866836</v>
       </c>
       <c r="B7" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 52894-2025 artfynd.xlsx
+++ b/artfynd/A 52894-2025 artfynd.xlsx
@@ -1208,7 +1208,7 @@
         <v>129866836</v>
       </c>
       <c r="B7" t="n">
-        <v>98920</v>
+        <v>98833</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
